--- a/uploads/registros.xlsx
+++ b/uploads/registros.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,6 +530,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="O2" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -578,6 +581,9 @@
       <c r="L3" t="n">
         <v>57.06</v>
       </c>
+      <c r="O3" t="n">
+        <v>2971</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -626,6 +632,9 @@
       <c r="L4" t="n">
         <v>4512.07</v>
       </c>
+      <c r="O4" t="n">
+        <v>4005</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -674,6 +683,9 @@
       <c r="L5" t="n">
         <v>0.24</v>
       </c>
+      <c r="O5" t="n">
+        <v>5053</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -722,6 +734,9 @@
       <c r="L6" t="n">
         <v>404</v>
       </c>
+      <c r="O6" t="n">
+        <v>4900</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -770,6 +785,9 @@
       <c r="L7" t="n">
         <v>299.91</v>
       </c>
+      <c r="O7" t="n">
+        <v>15151.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -817,6 +835,9 @@
       </c>
       <c r="L8" t="n">
         <v>300.77</v>
+      </c>
+      <c r="O8" t="n">
+        <v>15151.5</v>
       </c>
     </row>
     <row r="9">
